--- a/docs/plantillas/Rodatech - Maestro de productos.xlsx
+++ b/docs/plantillas/Rodatech - Maestro de productos.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="145">
   <si>
     <t>Maestro de productos · Rodatech</t>
   </si>
@@ -72,7 +72,31 @@
     <t>•   P.V. $ — YA VIENE CALCULADO: es el P.C. por 1.20, que es como lo tiene armado hoy. Si un producto es la excepción, escriba el valor encima y listo.</t>
   </si>
   <si>
-    <t>•   P.M. $ — el precio más bajo que acepta para ese producto. Es el piso: el sistema no va a dejar cotizar por debajo.</t>
+    <t>•   P.M. $ — el precio más bajo que acepta para ese producto. Es el PISO: el sistema no va a dejar cotizar por debajo. Si para usted P.M. quiere decir otra cosa —el precio al que ve que está el mercado— dígalo antes de cargar, porque para eso está la columna siguiente.</t>
+  </si>
+  <si>
+    <t>•   P. MERCADO $ — a cuánto ve que se está vendiendo en el mercado. Es solo una referencia para cotizar rápido; no bloquea nada ni sale en ningún documento.</t>
+  </si>
+  <si>
+    <t>•   PESO KG — cuánto pesa UNA unidad, en kilos, con hasta tres decimales (0.130). Es obligatorio para emitir la guía de remisión: sin peso, la guía hay que llenarla a mano cada vez.</t>
+  </si>
+  <si>
+    <t>•   UBICACION — dónde está en el almacén: el anaquel, el cajón. Lo que usted diría en voz alta para que alguien lo encuentre.</t>
+  </si>
+  <si>
+    <t>•   STOCK MAXIMO — a partir de cuántas unidades le sobra mercadería. El sistema le avisa del sobrestock, que es plata parada. Déjelo vacío si no quiere ese aviso.</t>
+  </si>
+  <si>
+    <t>•   COD. FABRICANTE — el otro código con el que también se conoce el producto, si lo hay. Sirve para encontrarlo buscando por cualquiera de los dos.</t>
+  </si>
+  <si>
+    <t>•   PROVEEDOR — a quién se lo compra habitualmente. Escriba el nombre tal como está dado de alta, o su RUC. Si no lo tenemos registrado, el producto entra igual y se lo avisamos para darlo de alta bien.</t>
+  </si>
+  <si>
+    <t>Las columnas nuevas puede llenarlas después</t>
+  </si>
+  <si>
+    <t>Si ahora no tiene el peso o la ubicación de todo, mande el archivo igual. Cuando los tenga, vuelva a subirlo: una columna en blanco NO borra lo que ya se cargó, solo se aplican las celdas que traigan dato.</t>
   </si>
   <si>
     <t>Lo que NO tiene que hacer</t>
@@ -421,6 +445,24 @@
   </si>
   <si>
     <t>P.M. $</t>
+  </si>
+  <si>
+    <t>P. MERCADO $</t>
+  </si>
+  <si>
+    <t>PESO KG</t>
+  </si>
+  <si>
+    <t>UBICACION</t>
+  </si>
+  <si>
+    <t>STOCK MAXIMO</t>
+  </si>
+  <si>
+    <t>COD. FABRICANTE</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
   </si>
   <si>
     <t>6205-2RS1/C3</t>
@@ -436,8 +478,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -511,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -531,6 +574,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -898,7 +944,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4C73"/>
   </sheetPr>
-  <dimension ref="B2:B24"/>
+  <dimension ref="B2:B33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -965,59 +1011,104 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>17</v>
+    <row r="21" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>19</v>
+    <row r="24" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1036,388 +1127,388 @@
   <sheetData>
     <row r="1" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" t="s">
         <v>46</v>
       </c>
-      <c r="I2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R2" t="s">
-        <v>55</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
       <c r="T2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="U2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="W2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="M3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="R3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="S3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="T3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="U3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="V3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="W3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="N4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="Q4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="S4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="T4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="U4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="W4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="Q5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="W5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="O6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="P6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="Q6" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="W6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="W7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="W8" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="W9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="W10" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="W11" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W12" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W13" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W14" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W15" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="23:23" x14ac:dyDescent="0.25">
       <c r="W16" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +1522,7 @@
   <sheetPr>
     <tabColor rgb="FFF2E307"/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1441,55 +1532,78 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F2" s="6">
         <v>35</v>
@@ -1506,22 +1620,25 @@
       <c r="J2" s="7">
         <v>3.86</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="7"/>
+      <c r="L2" s="9"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F3" s="6">
         <v>12</v>
@@ -1538,22 +1655,25 @@
       <c r="J3" s="7">
         <v>11.96</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="7"/>
+      <c r="L3" s="9"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F4" s="6">
         <v>8</v>
@@ -1570,8 +1690,11 @@
       <c r="J4" s="7">
         <v>13.79</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="7"/>
+      <c r="L4" s="9"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="7"/>
@@ -1580,8 +1703,11 @@
         <v/>
       </c>
       <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="7"/>
+      <c r="L5" s="9"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="7"/>
@@ -1590,8 +1716,11 @@
         <v/>
       </c>
       <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="7"/>
+      <c r="L6" s="9"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="7"/>
@@ -1600,8 +1729,11 @@
         <v/>
       </c>
       <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="7"/>
+      <c r="L7" s="9"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="7"/>
@@ -1610,8 +1742,11 @@
         <v/>
       </c>
       <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="7"/>
+      <c r="L8" s="9"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="7"/>
@@ -1620,8 +1755,11 @@
         <v/>
       </c>
       <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="7"/>
+      <c r="L9" s="9"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="7"/>
@@ -1630,8 +1768,11 @@
         <v/>
       </c>
       <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="7"/>
+      <c r="L10" s="9"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="7"/>
@@ -1640,8 +1781,11 @@
         <v/>
       </c>
       <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="7"/>
+      <c r="L11" s="9"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="7"/>
@@ -1650,8 +1794,11 @@
         <v/>
       </c>
       <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="7"/>
+      <c r="L12" s="9"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="7"/>
@@ -1660,8 +1807,11 @@
         <v/>
       </c>
       <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="7"/>
@@ -1670,8 +1820,11 @@
         <v/>
       </c>
       <c r="J14" s="7"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="7"/>
+      <c r="L14" s="9"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="7"/>
@@ -1680,8 +1833,11 @@
         <v/>
       </c>
       <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="7"/>
+      <c r="L15" s="9"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="7"/>
@@ -1690,8 +1846,11 @@
         <v/>
       </c>
       <c r="J16" s="7"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="7"/>
+      <c r="L16" s="9"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="7"/>
@@ -1700,8 +1859,11 @@
         <v/>
       </c>
       <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="7"/>
+      <c r="L17" s="9"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="7"/>
@@ -1710,8 +1872,11 @@
         <v/>
       </c>
       <c r="J18" s="7"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="7"/>
+      <c r="L18" s="9"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="7"/>
@@ -1720,8 +1885,11 @@
         <v/>
       </c>
       <c r="J19" s="7"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="7"/>
+      <c r="L19" s="9"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="7"/>
@@ -1730,8 +1898,11 @@
         <v/>
       </c>
       <c r="J20" s="7"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="7"/>
+      <c r="L20" s="9"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="7"/>
@@ -1740,8 +1911,11 @@
         <v/>
       </c>
       <c r="J21" s="7"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="7"/>
+      <c r="L21" s="9"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="7"/>
@@ -1750,8 +1924,11 @@
         <v/>
       </c>
       <c r="J22" s="7"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K22" s="7"/>
+      <c r="L22" s="9"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="7"/>
@@ -1760,8 +1937,11 @@
         <v/>
       </c>
       <c r="J23" s="7"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="7"/>
+      <c r="L23" s="9"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="7"/>
@@ -1770,8 +1950,11 @@
         <v/>
       </c>
       <c r="J24" s="7"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K24" s="7"/>
+      <c r="L24" s="9"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="7"/>
@@ -1780,8 +1963,11 @@
         <v/>
       </c>
       <c r="J25" s="7"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K25" s="7"/>
+      <c r="L25" s="9"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="7"/>
@@ -1790,8 +1976,11 @@
         <v/>
       </c>
       <c r="J26" s="7"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K26" s="7"/>
+      <c r="L26" s="9"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="7"/>
@@ -1800,8 +1989,11 @@
         <v/>
       </c>
       <c r="J27" s="7"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="7"/>
+      <c r="L27" s="9"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="7"/>
@@ -1810,8 +2002,11 @@
         <v/>
       </c>
       <c r="J28" s="7"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="7"/>
+      <c r="L28" s="9"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="7"/>
@@ -1820,8 +2015,11 @@
         <v/>
       </c>
       <c r="J29" s="7"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="7"/>
+      <c r="L29" s="9"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="7"/>
@@ -1830,8 +2028,11 @@
         <v/>
       </c>
       <c r="J30" s="7"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="7"/>
+      <c r="L30" s="9"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="7"/>
@@ -1840,8 +2041,11 @@
         <v/>
       </c>
       <c r="J31" s="7"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="7"/>
+      <c r="L31" s="9"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="7"/>
@@ -1850,8 +2054,11 @@
         <v/>
       </c>
       <c r="J32" s="7"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="7"/>
+      <c r="L32" s="9"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="7"/>
@@ -1860,8 +2067,11 @@
         <v/>
       </c>
       <c r="J33" s="7"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="7"/>
+      <c r="L33" s="9"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="7"/>
@@ -1870,8 +2080,11 @@
         <v/>
       </c>
       <c r="J34" s="7"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="7"/>
+      <c r="L34" s="9"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="7"/>
@@ -1880,8 +2093,11 @@
         <v/>
       </c>
       <c r="J35" s="7"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K35" s="7"/>
+      <c r="L35" s="9"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="7"/>
@@ -1890,8 +2106,11 @@
         <v/>
       </c>
       <c r="J36" s="7"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K36" s="7"/>
+      <c r="L36" s="9"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="7"/>
@@ -1900,8 +2119,11 @@
         <v/>
       </c>
       <c r="J37" s="7"/>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K37" s="7"/>
+      <c r="L37" s="9"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="7"/>
@@ -1910,8 +2132,11 @@
         <v/>
       </c>
       <c r="J38" s="7"/>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K38" s="7"/>
+      <c r="L38" s="9"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="7"/>
@@ -1920,8 +2145,11 @@
         <v/>
       </c>
       <c r="J39" s="7"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K39" s="7"/>
+      <c r="L39" s="9"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="7"/>
@@ -1930,8 +2158,11 @@
         <v/>
       </c>
       <c r="J40" s="7"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K40" s="7"/>
+      <c r="L40" s="9"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="7"/>
@@ -1940,8 +2171,11 @@
         <v/>
       </c>
       <c r="J41" s="7"/>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K41" s="7"/>
+      <c r="L41" s="9"/>
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="7"/>
@@ -1950,8 +2184,11 @@
         <v/>
       </c>
       <c r="J42" s="7"/>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K42" s="7"/>
+      <c r="L42" s="9"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="7"/>
@@ -1960,8 +2197,11 @@
         <v/>
       </c>
       <c r="J43" s="7"/>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K43" s="7"/>
+      <c r="L43" s="9"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="7"/>
@@ -1970,8 +2210,11 @@
         <v/>
       </c>
       <c r="J44" s="7"/>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K44" s="7"/>
+      <c r="L44" s="9"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="7"/>
@@ -1980,8 +2223,11 @@
         <v/>
       </c>
       <c r="J45" s="7"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K45" s="7"/>
+      <c r="L45" s="9"/>
+      <c r="N45" s="6"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="7"/>
@@ -1990,8 +2236,11 @@
         <v/>
       </c>
       <c r="J46" s="7"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K46" s="7"/>
+      <c r="L46" s="9"/>
+      <c r="N46" s="6"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="7"/>
@@ -2000,8 +2249,11 @@
         <v/>
       </c>
       <c r="J47" s="7"/>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K47" s="7"/>
+      <c r="L47" s="9"/>
+      <c r="N47" s="6"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="7"/>
@@ -2010,8 +2262,11 @@
         <v/>
       </c>
       <c r="J48" s="7"/>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K48" s="7"/>
+      <c r="L48" s="9"/>
+      <c r="N48" s="6"/>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="7"/>
@@ -2020,8 +2275,11 @@
         <v/>
       </c>
       <c r="J49" s="7"/>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K49" s="7"/>
+      <c r="L49" s="9"/>
+      <c r="N49" s="6"/>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="7"/>
@@ -2030,8 +2288,11 @@
         <v/>
       </c>
       <c r="J50" s="7"/>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K50" s="7"/>
+      <c r="L50" s="9"/>
+      <c r="N50" s="6"/>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="7"/>
@@ -2040,8 +2301,11 @@
         <v/>
       </c>
       <c r="J51" s="7"/>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K51" s="7"/>
+      <c r="L51" s="9"/>
+      <c r="N51" s="6"/>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="7"/>
@@ -2050,8 +2314,11 @@
         <v/>
       </c>
       <c r="J52" s="7"/>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K52" s="7"/>
+      <c r="L52" s="9"/>
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="7"/>
@@ -2060,8 +2327,11 @@
         <v/>
       </c>
       <c r="J53" s="7"/>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K53" s="7"/>
+      <c r="L53" s="9"/>
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="7"/>
@@ -2070,8 +2340,11 @@
         <v/>
       </c>
       <c r="J54" s="7"/>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K54" s="7"/>
+      <c r="L54" s="9"/>
+      <c r="N54" s="6"/>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="7"/>
@@ -2080,8 +2353,11 @@
         <v/>
       </c>
       <c r="J55" s="7"/>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K55" s="7"/>
+      <c r="L55" s="9"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="7"/>
@@ -2090,8 +2366,11 @@
         <v/>
       </c>
       <c r="J56" s="7"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K56" s="7"/>
+      <c r="L56" s="9"/>
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="7"/>
@@ -2100,8 +2379,11 @@
         <v/>
       </c>
       <c r="J57" s="7"/>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K57" s="7"/>
+      <c r="L57" s="9"/>
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="7"/>
@@ -2110,8 +2392,11 @@
         <v/>
       </c>
       <c r="J58" s="7"/>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K58" s="7"/>
+      <c r="L58" s="9"/>
+      <c r="N58" s="6"/>
+    </row>
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="7"/>
@@ -2120,8 +2405,11 @@
         <v/>
       </c>
       <c r="J59" s="7"/>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K59" s="7"/>
+      <c r="L59" s="9"/>
+      <c r="N59" s="6"/>
+    </row>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="7"/>
@@ -2130,8 +2418,11 @@
         <v/>
       </c>
       <c r="J60" s="7"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K60" s="7"/>
+      <c r="L60" s="9"/>
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="7"/>
@@ -2140,8 +2431,11 @@
         <v/>
       </c>
       <c r="J61" s="7"/>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K61" s="7"/>
+      <c r="L61" s="9"/>
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="7"/>
@@ -2150,8 +2444,11 @@
         <v/>
       </c>
       <c r="J62" s="7"/>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K62" s="7"/>
+      <c r="L62" s="9"/>
+      <c r="N62" s="6"/>
+    </row>
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="7"/>
@@ -2160,8 +2457,11 @@
         <v/>
       </c>
       <c r="J63" s="7"/>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K63" s="7"/>
+      <c r="L63" s="9"/>
+      <c r="N63" s="6"/>
+    </row>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="7"/>
@@ -2170,8 +2470,11 @@
         <v/>
       </c>
       <c r="J64" s="7"/>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K64" s="7"/>
+      <c r="L64" s="9"/>
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="7"/>
@@ -2180,8 +2483,11 @@
         <v/>
       </c>
       <c r="J65" s="7"/>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K65" s="7"/>
+      <c r="L65" s="9"/>
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="7"/>
@@ -2190,8 +2496,11 @@
         <v/>
       </c>
       <c r="J66" s="7"/>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K66" s="7"/>
+      <c r="L66" s="9"/>
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="7"/>
@@ -2200,8 +2509,11 @@
         <v/>
       </c>
       <c r="J67" s="7"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K67" s="7"/>
+      <c r="L67" s="9"/>
+      <c r="N67" s="6"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="7"/>
@@ -2210,8 +2522,11 @@
         <v/>
       </c>
       <c r="J68" s="7"/>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K68" s="7"/>
+      <c r="L68" s="9"/>
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="7"/>
@@ -2220,8 +2535,11 @@
         <v/>
       </c>
       <c r="J69" s="7"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K69" s="7"/>
+      <c r="L69" s="9"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="7"/>
@@ -2230,8 +2548,11 @@
         <v/>
       </c>
       <c r="J70" s="7"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K70" s="7"/>
+      <c r="L70" s="9"/>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="7"/>
@@ -2240,8 +2561,11 @@
         <v/>
       </c>
       <c r="J71" s="7"/>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K71" s="7"/>
+      <c r="L71" s="9"/>
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="7"/>
@@ -2250,8 +2574,11 @@
         <v/>
       </c>
       <c r="J72" s="7"/>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K72" s="7"/>
+      <c r="L72" s="9"/>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="7"/>
@@ -2260,8 +2587,11 @@
         <v/>
       </c>
       <c r="J73" s="7"/>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K73" s="7"/>
+      <c r="L73" s="9"/>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="7"/>
@@ -2270,8 +2600,11 @@
         <v/>
       </c>
       <c r="J74" s="7"/>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K74" s="7"/>
+      <c r="L74" s="9"/>
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="7"/>
@@ -2280,8 +2613,11 @@
         <v/>
       </c>
       <c r="J75" s="7"/>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K75" s="7"/>
+      <c r="L75" s="9"/>
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="7"/>
@@ -2290,8 +2626,11 @@
         <v/>
       </c>
       <c r="J76" s="7"/>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K76" s="7"/>
+      <c r="L76" s="9"/>
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="7"/>
@@ -2300,8 +2639,11 @@
         <v/>
       </c>
       <c r="J77" s="7"/>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K77" s="7"/>
+      <c r="L77" s="9"/>
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="7"/>
@@ -2310,8 +2652,11 @@
         <v/>
       </c>
       <c r="J78" s="7"/>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K78" s="7"/>
+      <c r="L78" s="9"/>
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="7"/>
@@ -2320,8 +2665,11 @@
         <v/>
       </c>
       <c r="J79" s="7"/>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K79" s="7"/>
+      <c r="L79" s="9"/>
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="7"/>
@@ -2330,8 +2678,11 @@
         <v/>
       </c>
       <c r="J80" s="7"/>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K80" s="7"/>
+      <c r="L80" s="9"/>
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="7"/>
@@ -2340,8 +2691,11 @@
         <v/>
       </c>
       <c r="J81" s="7"/>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K81" s="7"/>
+      <c r="L81" s="9"/>
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="7"/>
@@ -2350,8 +2704,11 @@
         <v/>
       </c>
       <c r="J82" s="7"/>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K82" s="7"/>
+      <c r="L82" s="9"/>
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="7"/>
@@ -2360,8 +2717,11 @@
         <v/>
       </c>
       <c r="J83" s="7"/>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K83" s="7"/>
+      <c r="L83" s="9"/>
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="7"/>
@@ -2370,8 +2730,11 @@
         <v/>
       </c>
       <c r="J84" s="7"/>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K84" s="7"/>
+      <c r="L84" s="9"/>
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="7"/>
@@ -2380,8 +2743,11 @@
         <v/>
       </c>
       <c r="J85" s="7"/>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K85" s="7"/>
+      <c r="L85" s="9"/>
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="7"/>
@@ -2390,8 +2756,11 @@
         <v/>
       </c>
       <c r="J86" s="7"/>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K86" s="7"/>
+      <c r="L86" s="9"/>
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="7"/>
@@ -2400,8 +2769,11 @@
         <v/>
       </c>
       <c r="J87" s="7"/>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K87" s="7"/>
+      <c r="L87" s="9"/>
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="7"/>
@@ -2410,8 +2782,11 @@
         <v/>
       </c>
       <c r="J88" s="7"/>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K88" s="7"/>
+      <c r="L88" s="9"/>
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="7"/>
@@ -2420,8 +2795,11 @@
         <v/>
       </c>
       <c r="J89" s="7"/>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K89" s="7"/>
+      <c r="L89" s="9"/>
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="7"/>
@@ -2430,8 +2808,11 @@
         <v/>
       </c>
       <c r="J90" s="7"/>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K90" s="7"/>
+      <c r="L90" s="9"/>
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="7"/>
@@ -2440,8 +2821,11 @@
         <v/>
       </c>
       <c r="J91" s="7"/>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K91" s="7"/>
+      <c r="L91" s="9"/>
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="7"/>
@@ -2450,8 +2834,11 @@
         <v/>
       </c>
       <c r="J92" s="7"/>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K92" s="7"/>
+      <c r="L92" s="9"/>
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="7"/>
@@ -2460,8 +2847,11 @@
         <v/>
       </c>
       <c r="J93" s="7"/>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K93" s="7"/>
+      <c r="L93" s="9"/>
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="7"/>
@@ -2470,8 +2860,11 @@
         <v/>
       </c>
       <c r="J94" s="7"/>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K94" s="7"/>
+      <c r="L94" s="9"/>
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="7"/>
@@ -2480,8 +2873,11 @@
         <v/>
       </c>
       <c r="J95" s="7"/>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K95" s="7"/>
+      <c r="L95" s="9"/>
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="7"/>
@@ -2490,8 +2886,11 @@
         <v/>
       </c>
       <c r="J96" s="7"/>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K96" s="7"/>
+      <c r="L96" s="9"/>
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="7"/>
@@ -2500,8 +2899,11 @@
         <v/>
       </c>
       <c r="J97" s="7"/>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K97" s="7"/>
+      <c r="L97" s="9"/>
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="7"/>
@@ -2510,8 +2912,11 @@
         <v/>
       </c>
       <c r="J98" s="7"/>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K98" s="7"/>
+      <c r="L98" s="9"/>
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="7"/>
@@ -2520,8 +2925,11 @@
         <v/>
       </c>
       <c r="J99" s="7"/>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K99" s="7"/>
+      <c r="L99" s="9"/>
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="7"/>
@@ -2530,8 +2938,11 @@
         <v/>
       </c>
       <c r="J100" s="7"/>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K100" s="7"/>
+      <c r="L100" s="9"/>
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="7"/>
@@ -2540,8 +2951,11 @@
         <v/>
       </c>
       <c r="J101" s="7"/>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K101" s="7"/>
+      <c r="L101" s="9"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
       <c r="H102" s="7"/>
@@ -2550,8 +2964,11 @@
         <v/>
       </c>
       <c r="J102" s="7"/>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K102" s="7"/>
+      <c r="L102" s="9"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
       <c r="H103" s="7"/>
@@ -2560,8 +2977,11 @@
         <v/>
       </c>
       <c r="J103" s="7"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K103" s="7"/>
+      <c r="L103" s="9"/>
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="7"/>
@@ -2570,8 +2990,11 @@
         <v/>
       </c>
       <c r="J104" s="7"/>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K104" s="7"/>
+      <c r="L104" s="9"/>
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="7"/>
@@ -2580,8 +3003,11 @@
         <v/>
       </c>
       <c r="J105" s="7"/>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K105" s="7"/>
+      <c r="L105" s="9"/>
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="7"/>
@@ -2590,8 +3016,11 @@
         <v/>
       </c>
       <c r="J106" s="7"/>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K106" s="7"/>
+      <c r="L106" s="9"/>
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="7"/>
@@ -2600,8 +3029,11 @@
         <v/>
       </c>
       <c r="J107" s="7"/>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K107" s="7"/>
+      <c r="L107" s="9"/>
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="7"/>
@@ -2610,8 +3042,11 @@
         <v/>
       </c>
       <c r="J108" s="7"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K108" s="7"/>
+      <c r="L108" s="9"/>
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="7"/>
@@ -2620,8 +3055,11 @@
         <v/>
       </c>
       <c r="J109" s="7"/>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K109" s="7"/>
+      <c r="L109" s="9"/>
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="7"/>
@@ -2630,8 +3068,11 @@
         <v/>
       </c>
       <c r="J110" s="7"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K110" s="7"/>
+      <c r="L110" s="9"/>
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="7"/>
@@ -2640,8 +3081,11 @@
         <v/>
       </c>
       <c r="J111" s="7"/>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K111" s="7"/>
+      <c r="L111" s="9"/>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="7"/>
@@ -2650,8 +3094,11 @@
         <v/>
       </c>
       <c r="J112" s="7"/>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K112" s="7"/>
+      <c r="L112" s="9"/>
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="7"/>
@@ -2660,8 +3107,11 @@
         <v/>
       </c>
       <c r="J113" s="7"/>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K113" s="7"/>
+      <c r="L113" s="9"/>
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="7"/>
@@ -2670,8 +3120,11 @@
         <v/>
       </c>
       <c r="J114" s="7"/>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K114" s="7"/>
+      <c r="L114" s="9"/>
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="7"/>
@@ -2680,8 +3133,11 @@
         <v/>
       </c>
       <c r="J115" s="7"/>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K115" s="7"/>
+      <c r="L115" s="9"/>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="7"/>
@@ -2690,8 +3146,11 @@
         <v/>
       </c>
       <c r="J116" s="7"/>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K116" s="7"/>
+      <c r="L116" s="9"/>
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="7"/>
@@ -2700,8 +3159,11 @@
         <v/>
       </c>
       <c r="J117" s="7"/>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K117" s="7"/>
+      <c r="L117" s="9"/>
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="7"/>
@@ -2710,8 +3172,11 @@
         <v/>
       </c>
       <c r="J118" s="7"/>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K118" s="7"/>
+      <c r="L118" s="9"/>
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="7"/>
@@ -2720,8 +3185,11 @@
         <v/>
       </c>
       <c r="J119" s="7"/>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K119" s="7"/>
+      <c r="L119" s="9"/>
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F120" s="6"/>
       <c r="G120" s="6"/>
       <c r="H120" s="7"/>
@@ -2730,8 +3198,11 @@
         <v/>
       </c>
       <c r="J120" s="7"/>
-    </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K120" s="7"/>
+      <c r="L120" s="9"/>
+      <c r="N120" s="6"/>
+    </row>
+    <row r="121" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F121" s="6"/>
       <c r="G121" s="6"/>
       <c r="H121" s="7"/>
@@ -2740,8 +3211,11 @@
         <v/>
       </c>
       <c r="J121" s="7"/>
-    </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K121" s="7"/>
+      <c r="L121" s="9"/>
+      <c r="N121" s="6"/>
+    </row>
+    <row r="122" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="7"/>
@@ -2750,8 +3224,11 @@
         <v/>
       </c>
       <c r="J122" s="7"/>
-    </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K122" s="7"/>
+      <c r="L122" s="9"/>
+      <c r="N122" s="6"/>
+    </row>
+    <row r="123" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F123" s="6"/>
       <c r="G123" s="6"/>
       <c r="H123" s="7"/>
@@ -2760,8 +3237,11 @@
         <v/>
       </c>
       <c r="J123" s="7"/>
-    </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K123" s="7"/>
+      <c r="L123" s="9"/>
+      <c r="N123" s="6"/>
+    </row>
+    <row r="124" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="7"/>
@@ -2770,8 +3250,11 @@
         <v/>
       </c>
       <c r="J124" s="7"/>
-    </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K124" s="7"/>
+      <c r="L124" s="9"/>
+      <c r="N124" s="6"/>
+    </row>
+    <row r="125" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F125" s="6"/>
       <c r="G125" s="6"/>
       <c r="H125" s="7"/>
@@ -2780,8 +3263,11 @@
         <v/>
       </c>
       <c r="J125" s="7"/>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K125" s="7"/>
+      <c r="L125" s="9"/>
+      <c r="N125" s="6"/>
+    </row>
+    <row r="126" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="7"/>
@@ -2790,8 +3276,11 @@
         <v/>
       </c>
       <c r="J126" s="7"/>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K126" s="7"/>
+      <c r="L126" s="9"/>
+      <c r="N126" s="6"/>
+    </row>
+    <row r="127" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="7"/>
@@ -2800,8 +3289,11 @@
         <v/>
       </c>
       <c r="J127" s="7"/>
-    </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K127" s="7"/>
+      <c r="L127" s="9"/>
+      <c r="N127" s="6"/>
+    </row>
+    <row r="128" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="7"/>
@@ -2810,8 +3302,11 @@
         <v/>
       </c>
       <c r="J128" s="7"/>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K128" s="7"/>
+      <c r="L128" s="9"/>
+      <c r="N128" s="6"/>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
       <c r="H129" s="7"/>
@@ -2820,8 +3315,11 @@
         <v/>
       </c>
       <c r="J129" s="7"/>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K129" s="7"/>
+      <c r="L129" s="9"/>
+      <c r="N129" s="6"/>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
       <c r="H130" s="7"/>
@@ -2830,8 +3328,11 @@
         <v/>
       </c>
       <c r="J130" s="7"/>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K130" s="7"/>
+      <c r="L130" s="9"/>
+      <c r="N130" s="6"/>
+    </row>
+    <row r="131" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
       <c r="H131" s="7"/>
@@ -2840,8 +3341,11 @@
         <v/>
       </c>
       <c r="J131" s="7"/>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K131" s="7"/>
+      <c r="L131" s="9"/>
+      <c r="N131" s="6"/>
+    </row>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
       <c r="H132" s="7"/>
@@ -2850,8 +3354,11 @@
         <v/>
       </c>
       <c r="J132" s="7"/>
-    </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K132" s="7"/>
+      <c r="L132" s="9"/>
+      <c r="N132" s="6"/>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
       <c r="H133" s="7"/>
@@ -2860,8 +3367,11 @@
         <v/>
       </c>
       <c r="J133" s="7"/>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K133" s="7"/>
+      <c r="L133" s="9"/>
+      <c r="N133" s="6"/>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
       <c r="H134" s="7"/>
@@ -2870,8 +3380,11 @@
         <v/>
       </c>
       <c r="J134" s="7"/>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K134" s="7"/>
+      <c r="L134" s="9"/>
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
       <c r="H135" s="7"/>
@@ -2880,8 +3393,11 @@
         <v/>
       </c>
       <c r="J135" s="7"/>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K135" s="7"/>
+      <c r="L135" s="9"/>
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="7"/>
@@ -2890,8 +3406,11 @@
         <v/>
       </c>
       <c r="J136" s="7"/>
-    </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K136" s="7"/>
+      <c r="L136" s="9"/>
+      <c r="N136" s="6"/>
+    </row>
+    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
       <c r="H137" s="7"/>
@@ -2900,8 +3419,11 @@
         <v/>
       </c>
       <c r="J137" s="7"/>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K137" s="7"/>
+      <c r="L137" s="9"/>
+      <c r="N137" s="6"/>
+    </row>
+    <row r="138" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F138" s="6"/>
       <c r="G138" s="6"/>
       <c r="H138" s="7"/>
@@ -2910,8 +3432,11 @@
         <v/>
       </c>
       <c r="J138" s="7"/>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K138" s="7"/>
+      <c r="L138" s="9"/>
+      <c r="N138" s="6"/>
+    </row>
+    <row r="139" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
       <c r="H139" s="7"/>
@@ -2920,8 +3445,11 @@
         <v/>
       </c>
       <c r="J139" s="7"/>
-    </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K139" s="7"/>
+      <c r="L139" s="9"/>
+      <c r="N139" s="6"/>
+    </row>
+    <row r="140" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F140" s="6"/>
       <c r="G140" s="6"/>
       <c r="H140" s="7"/>
@@ -2930,8 +3458,11 @@
         <v/>
       </c>
       <c r="J140" s="7"/>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K140" s="7"/>
+      <c r="L140" s="9"/>
+      <c r="N140" s="6"/>
+    </row>
+    <row r="141" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="7"/>
@@ -2940,8 +3471,11 @@
         <v/>
       </c>
       <c r="J141" s="7"/>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K141" s="7"/>
+      <c r="L141" s="9"/>
+      <c r="N141" s="6"/>
+    </row>
+    <row r="142" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F142" s="6"/>
       <c r="G142" s="6"/>
       <c r="H142" s="7"/>
@@ -2950,8 +3484,11 @@
         <v/>
       </c>
       <c r="J142" s="7"/>
-    </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K142" s="7"/>
+      <c r="L142" s="9"/>
+      <c r="N142" s="6"/>
+    </row>
+    <row r="143" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
       <c r="H143" s="7"/>
@@ -2960,8 +3497,11 @@
         <v/>
       </c>
       <c r="J143" s="7"/>
-    </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K143" s="7"/>
+      <c r="L143" s="9"/>
+      <c r="N143" s="6"/>
+    </row>
+    <row r="144" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F144" s="6"/>
       <c r="G144" s="6"/>
       <c r="H144" s="7"/>
@@ -2970,8 +3510,11 @@
         <v/>
       </c>
       <c r="J144" s="7"/>
-    </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K144" s="7"/>
+      <c r="L144" s="9"/>
+      <c r="N144" s="6"/>
+    </row>
+    <row r="145" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
       <c r="H145" s="7"/>
@@ -2980,8 +3523,11 @@
         <v/>
       </c>
       <c r="J145" s="7"/>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K145" s="7"/>
+      <c r="L145" s="9"/>
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
       <c r="H146" s="7"/>
@@ -2990,8 +3536,11 @@
         <v/>
       </c>
       <c r="J146" s="7"/>
-    </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K146" s="7"/>
+      <c r="L146" s="9"/>
+      <c r="N146" s="6"/>
+    </row>
+    <row r="147" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
       <c r="H147" s="7"/>
@@ -3000,8 +3549,11 @@
         <v/>
       </c>
       <c r="J147" s="7"/>
-    </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K147" s="7"/>
+      <c r="L147" s="9"/>
+      <c r="N147" s="6"/>
+    </row>
+    <row r="148" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
       <c r="H148" s="7"/>
@@ -3010,8 +3562,11 @@
         <v/>
       </c>
       <c r="J148" s="7"/>
-    </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K148" s="7"/>
+      <c r="L148" s="9"/>
+      <c r="N148" s="6"/>
+    </row>
+    <row r="149" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
       <c r="H149" s="7"/>
@@ -3020,8 +3575,11 @@
         <v/>
       </c>
       <c r="J149" s="7"/>
-    </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K149" s="7"/>
+      <c r="L149" s="9"/>
+      <c r="N149" s="6"/>
+    </row>
+    <row r="150" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
       <c r="H150" s="7"/>
@@ -3030,8 +3588,11 @@
         <v/>
       </c>
       <c r="J150" s="7"/>
-    </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K150" s="7"/>
+      <c r="L150" s="9"/>
+      <c r="N150" s="6"/>
+    </row>
+    <row r="151" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
       <c r="H151" s="7"/>
@@ -3040,8 +3601,11 @@
         <v/>
       </c>
       <c r="J151" s="7"/>
-    </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K151" s="7"/>
+      <c r="L151" s="9"/>
+      <c r="N151" s="6"/>
+    </row>
+    <row r="152" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
       <c r="H152" s="7"/>
@@ -3050,8 +3614,11 @@
         <v/>
       </c>
       <c r="J152" s="7"/>
-    </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K152" s="7"/>
+      <c r="L152" s="9"/>
+      <c r="N152" s="6"/>
+    </row>
+    <row r="153" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
       <c r="H153" s="7"/>
@@ -3060,8 +3627,11 @@
         <v/>
       </c>
       <c r="J153" s="7"/>
-    </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K153" s="7"/>
+      <c r="L153" s="9"/>
+      <c r="N153" s="6"/>
+    </row>
+    <row r="154" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
       <c r="H154" s="7"/>
@@ -3070,8 +3640,11 @@
         <v/>
       </c>
       <c r="J154" s="7"/>
-    </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K154" s="7"/>
+      <c r="L154" s="9"/>
+      <c r="N154" s="6"/>
+    </row>
+    <row r="155" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F155" s="6"/>
       <c r="G155" s="6"/>
       <c r="H155" s="7"/>
@@ -3080,8 +3653,11 @@
         <v/>
       </c>
       <c r="J155" s="7"/>
-    </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K155" s="7"/>
+      <c r="L155" s="9"/>
+      <c r="N155" s="6"/>
+    </row>
+    <row r="156" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F156" s="6"/>
       <c r="G156" s="6"/>
       <c r="H156" s="7"/>
@@ -3090,8 +3666,11 @@
         <v/>
       </c>
       <c r="J156" s="7"/>
-    </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K156" s="7"/>
+      <c r="L156" s="9"/>
+      <c r="N156" s="6"/>
+    </row>
+    <row r="157" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F157" s="6"/>
       <c r="G157" s="6"/>
       <c r="H157" s="7"/>
@@ -3100,8 +3679,11 @@
         <v/>
       </c>
       <c r="J157" s="7"/>
-    </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K157" s="7"/>
+      <c r="L157" s="9"/>
+      <c r="N157" s="6"/>
+    </row>
+    <row r="158" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
       <c r="H158" s="7"/>
@@ -3110,8 +3692,11 @@
         <v/>
       </c>
       <c r="J158" s="7"/>
-    </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K158" s="7"/>
+      <c r="L158" s="9"/>
+      <c r="N158" s="6"/>
+    </row>
+    <row r="159" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
       <c r="H159" s="7"/>
@@ -3120,8 +3705,11 @@
         <v/>
       </c>
       <c r="J159" s="7"/>
-    </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K159" s="7"/>
+      <c r="L159" s="9"/>
+      <c r="N159" s="6"/>
+    </row>
+    <row r="160" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
       <c r="H160" s="7"/>
@@ -3130,8 +3718,11 @@
         <v/>
       </c>
       <c r="J160" s="7"/>
-    </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K160" s="7"/>
+      <c r="L160" s="9"/>
+      <c r="N160" s="6"/>
+    </row>
+    <row r="161" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
       <c r="H161" s="7"/>
@@ -3140,8 +3731,11 @@
         <v/>
       </c>
       <c r="J161" s="7"/>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K161" s="7"/>
+      <c r="L161" s="9"/>
+      <c r="N161" s="6"/>
+    </row>
+    <row r="162" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
       <c r="H162" s="7"/>
@@ -3150,8 +3744,11 @@
         <v/>
       </c>
       <c r="J162" s="7"/>
-    </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K162" s="7"/>
+      <c r="L162" s="9"/>
+      <c r="N162" s="6"/>
+    </row>
+    <row r="163" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
       <c r="H163" s="7"/>
@@ -3160,8 +3757,11 @@
         <v/>
       </c>
       <c r="J163" s="7"/>
-    </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K163" s="7"/>
+      <c r="L163" s="9"/>
+      <c r="N163" s="6"/>
+    </row>
+    <row r="164" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
       <c r="H164" s="7"/>
@@ -3170,8 +3770,11 @@
         <v/>
       </c>
       <c r="J164" s="7"/>
-    </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K164" s="7"/>
+      <c r="L164" s="9"/>
+      <c r="N164" s="6"/>
+    </row>
+    <row r="165" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
       <c r="H165" s="7"/>
@@ -3180,8 +3783,11 @@
         <v/>
       </c>
       <c r="J165" s="7"/>
-    </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K165" s="7"/>
+      <c r="L165" s="9"/>
+      <c r="N165" s="6"/>
+    </row>
+    <row r="166" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
       <c r="H166" s="7"/>
@@ -3190,8 +3796,11 @@
         <v/>
       </c>
       <c r="J166" s="7"/>
-    </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K166" s="7"/>
+      <c r="L166" s="9"/>
+      <c r="N166" s="6"/>
+    </row>
+    <row r="167" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
       <c r="H167" s="7"/>
@@ -3200,8 +3809,11 @@
         <v/>
       </c>
       <c r="J167" s="7"/>
-    </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K167" s="7"/>
+      <c r="L167" s="9"/>
+      <c r="N167" s="6"/>
+    </row>
+    <row r="168" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
       <c r="H168" s="7"/>
@@ -3210,8 +3822,11 @@
         <v/>
       </c>
       <c r="J168" s="7"/>
-    </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K168" s="7"/>
+      <c r="L168" s="9"/>
+      <c r="N168" s="6"/>
+    </row>
+    <row r="169" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
       <c r="H169" s="7"/>
@@ -3220,8 +3835,11 @@
         <v/>
       </c>
       <c r="J169" s="7"/>
-    </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K169" s="7"/>
+      <c r="L169" s="9"/>
+      <c r="N169" s="6"/>
+    </row>
+    <row r="170" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
       <c r="H170" s="7"/>
@@ -3230,8 +3848,11 @@
         <v/>
       </c>
       <c r="J170" s="7"/>
-    </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K170" s="7"/>
+      <c r="L170" s="9"/>
+      <c r="N170" s="6"/>
+    </row>
+    <row r="171" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
       <c r="H171" s="7"/>
@@ -3240,8 +3861,11 @@
         <v/>
       </c>
       <c r="J171" s="7"/>
-    </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K171" s="7"/>
+      <c r="L171" s="9"/>
+      <c r="N171" s="6"/>
+    </row>
+    <row r="172" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
       <c r="H172" s="7"/>
@@ -3250,8 +3874,11 @@
         <v/>
       </c>
       <c r="J172" s="7"/>
-    </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K172" s="7"/>
+      <c r="L172" s="9"/>
+      <c r="N172" s="6"/>
+    </row>
+    <row r="173" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="7"/>
@@ -3260,8 +3887,11 @@
         <v/>
       </c>
       <c r="J173" s="7"/>
-    </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K173" s="7"/>
+      <c r="L173" s="9"/>
+      <c r="N173" s="6"/>
+    </row>
+    <row r="174" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
       <c r="H174" s="7"/>
@@ -3270,8 +3900,11 @@
         <v/>
       </c>
       <c r="J174" s="7"/>
-    </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K174" s="7"/>
+      <c r="L174" s="9"/>
+      <c r="N174" s="6"/>
+    </row>
+    <row r="175" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F175" s="6"/>
       <c r="G175" s="6"/>
       <c r="H175" s="7"/>
@@ -3280,8 +3913,11 @@
         <v/>
       </c>
       <c r="J175" s="7"/>
-    </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K175" s="7"/>
+      <c r="L175" s="9"/>
+      <c r="N175" s="6"/>
+    </row>
+    <row r="176" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
       <c r="H176" s="7"/>
@@ -3290,8 +3926,11 @@
         <v/>
       </c>
       <c r="J176" s="7"/>
-    </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K176" s="7"/>
+      <c r="L176" s="9"/>
+      <c r="N176" s="6"/>
+    </row>
+    <row r="177" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F177" s="6"/>
       <c r="G177" s="6"/>
       <c r="H177" s="7"/>
@@ -3300,8 +3939,11 @@
         <v/>
       </c>
       <c r="J177" s="7"/>
-    </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K177" s="7"/>
+      <c r="L177" s="9"/>
+      <c r="N177" s="6"/>
+    </row>
+    <row r="178" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F178" s="6"/>
       <c r="G178" s="6"/>
       <c r="H178" s="7"/>
@@ -3310,8 +3952,11 @@
         <v/>
       </c>
       <c r="J178" s="7"/>
-    </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K178" s="7"/>
+      <c r="L178" s="9"/>
+      <c r="N178" s="6"/>
+    </row>
+    <row r="179" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
       <c r="H179" s="7"/>
@@ -3320,8 +3965,11 @@
         <v/>
       </c>
       <c r="J179" s="7"/>
-    </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K179" s="7"/>
+      <c r="L179" s="9"/>
+      <c r="N179" s="6"/>
+    </row>
+    <row r="180" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F180" s="6"/>
       <c r="G180" s="6"/>
       <c r="H180" s="7"/>
@@ -3330,8 +3978,11 @@
         <v/>
       </c>
       <c r="J180" s="7"/>
-    </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K180" s="7"/>
+      <c r="L180" s="9"/>
+      <c r="N180" s="6"/>
+    </row>
+    <row r="181" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F181" s="6"/>
       <c r="G181" s="6"/>
       <c r="H181" s="7"/>
@@ -3340,8 +3991,11 @@
         <v/>
       </c>
       <c r="J181" s="7"/>
-    </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K181" s="7"/>
+      <c r="L181" s="9"/>
+      <c r="N181" s="6"/>
+    </row>
+    <row r="182" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F182" s="6"/>
       <c r="G182" s="6"/>
       <c r="H182" s="7"/>
@@ -3350,8 +4004,11 @@
         <v/>
       </c>
       <c r="J182" s="7"/>
-    </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K182" s="7"/>
+      <c r="L182" s="9"/>
+      <c r="N182" s="6"/>
+    </row>
+    <row r="183" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F183" s="6"/>
       <c r="G183" s="6"/>
       <c r="H183" s="7"/>
@@ -3360,8 +4017,11 @@
         <v/>
       </c>
       <c r="J183" s="7"/>
-    </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K183" s="7"/>
+      <c r="L183" s="9"/>
+      <c r="N183" s="6"/>
+    </row>
+    <row r="184" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F184" s="6"/>
       <c r="G184" s="6"/>
       <c r="H184" s="7"/>
@@ -3370,8 +4030,11 @@
         <v/>
       </c>
       <c r="J184" s="7"/>
-    </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K184" s="7"/>
+      <c r="L184" s="9"/>
+      <c r="N184" s="6"/>
+    </row>
+    <row r="185" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
       <c r="H185" s="7"/>
@@ -3380,8 +4043,11 @@
         <v/>
       </c>
       <c r="J185" s="7"/>
-    </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K185" s="7"/>
+      <c r="L185" s="9"/>
+      <c r="N185" s="6"/>
+    </row>
+    <row r="186" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
       <c r="H186" s="7"/>
@@ -3390,8 +4056,11 @@
         <v/>
       </c>
       <c r="J186" s="7"/>
-    </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K186" s="7"/>
+      <c r="L186" s="9"/>
+      <c r="N186" s="6"/>
+    </row>
+    <row r="187" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
       <c r="H187" s="7"/>
@@ -3400,8 +4069,11 @@
         <v/>
       </c>
       <c r="J187" s="7"/>
-    </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K187" s="7"/>
+      <c r="L187" s="9"/>
+      <c r="N187" s="6"/>
+    </row>
+    <row r="188" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
       <c r="H188" s="7"/>
@@ -3410,8 +4082,11 @@
         <v/>
       </c>
       <c r="J188" s="7"/>
-    </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K188" s="7"/>
+      <c r="L188" s="9"/>
+      <c r="N188" s="6"/>
+    </row>
+    <row r="189" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
       <c r="H189" s="7"/>
@@ -3420,8 +4095,11 @@
         <v/>
       </c>
       <c r="J189" s="7"/>
-    </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K189" s="7"/>
+      <c r="L189" s="9"/>
+      <c r="N189" s="6"/>
+    </row>
+    <row r="190" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
       <c r="H190" s="7"/>
@@ -3430,8 +4108,11 @@
         <v/>
       </c>
       <c r="J190" s="7"/>
-    </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K190" s="7"/>
+      <c r="L190" s="9"/>
+      <c r="N190" s="6"/>
+    </row>
+    <row r="191" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F191" s="6"/>
       <c r="G191" s="6"/>
       <c r="H191" s="7"/>
@@ -3440,8 +4121,11 @@
         <v/>
       </c>
       <c r="J191" s="7"/>
-    </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K191" s="7"/>
+      <c r="L191" s="9"/>
+      <c r="N191" s="6"/>
+    </row>
+    <row r="192" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F192" s="6"/>
       <c r="G192" s="6"/>
       <c r="H192" s="7"/>
@@ -3450,8 +4134,11 @@
         <v/>
       </c>
       <c r="J192" s="7"/>
-    </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K192" s="7"/>
+      <c r="L192" s="9"/>
+      <c r="N192" s="6"/>
+    </row>
+    <row r="193" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F193" s="6"/>
       <c r="G193" s="6"/>
       <c r="H193" s="7"/>
@@ -3460,8 +4147,11 @@
         <v/>
       </c>
       <c r="J193" s="7"/>
-    </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K193" s="7"/>
+      <c r="L193" s="9"/>
+      <c r="N193" s="6"/>
+    </row>
+    <row r="194" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F194" s="6"/>
       <c r="G194" s="6"/>
       <c r="H194" s="7"/>
@@ -3470,8 +4160,11 @@
         <v/>
       </c>
       <c r="J194" s="7"/>
-    </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K194" s="7"/>
+      <c r="L194" s="9"/>
+      <c r="N194" s="6"/>
+    </row>
+    <row r="195" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F195" s="6"/>
       <c r="G195" s="6"/>
       <c r="H195" s="7"/>
@@ -3480,8 +4173,11 @@
         <v/>
       </c>
       <c r="J195" s="7"/>
-    </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K195" s="7"/>
+      <c r="L195" s="9"/>
+      <c r="N195" s="6"/>
+    </row>
+    <row r="196" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F196" s="6"/>
       <c r="G196" s="6"/>
       <c r="H196" s="7"/>
@@ -3490,8 +4186,11 @@
         <v/>
       </c>
       <c r="J196" s="7"/>
-    </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K196" s="7"/>
+      <c r="L196" s="9"/>
+      <c r="N196" s="6"/>
+    </row>
+    <row r="197" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F197" s="6"/>
       <c r="G197" s="6"/>
       <c r="H197" s="7"/>
@@ -3500,8 +4199,11 @@
         <v/>
       </c>
       <c r="J197" s="7"/>
-    </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K197" s="7"/>
+      <c r="L197" s="9"/>
+      <c r="N197" s="6"/>
+    </row>
+    <row r="198" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F198" s="6"/>
       <c r="G198" s="6"/>
       <c r="H198" s="7"/>
@@ -3510,8 +4212,11 @@
         <v/>
       </c>
       <c r="J198" s="7"/>
-    </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K198" s="7"/>
+      <c r="L198" s="9"/>
+      <c r="N198" s="6"/>
+    </row>
+    <row r="199" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F199" s="6"/>
       <c r="G199" s="6"/>
       <c r="H199" s="7"/>
@@ -3520,8 +4225,11 @@
         <v/>
       </c>
       <c r="J199" s="7"/>
-    </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K199" s="7"/>
+      <c r="L199" s="9"/>
+      <c r="N199" s="6"/>
+    </row>
+    <row r="200" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F200" s="6"/>
       <c r="G200" s="6"/>
       <c r="H200" s="7"/>
@@ -3530,8 +4238,11 @@
         <v/>
       </c>
       <c r="J200" s="7"/>
-    </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K200" s="7"/>
+      <c r="L200" s="9"/>
+      <c r="N200" s="6"/>
+    </row>
+    <row r="201" spans="2:14" x14ac:dyDescent="0.25">
       <c r="F201" s="6"/>
       <c r="G201" s="6"/>
       <c r="H201" s="7"/>
@@ -3540,9 +4251,12 @@
         <v/>
       </c>
       <c r="J201" s="7"/>
+      <c r="K201" s="7"/>
+      <c r="L201" s="9"/>
+      <c r="N201" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:P1"/>
   <conditionalFormatting sqref="A2:A201">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($A2&lt;&gt;"",COUNTIF($A$2:$A$201,$A2)&gt;1)</formula>
